--- a/data/trans_camb/IP41-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP41-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 17,05</t>
+          <t>-3,61; 15,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 17,53</t>
+          <t>-3,84; 17,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-80,6; -66,21</t>
+          <t>-81,56; -66,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,4; 8,5</t>
+          <t>-10,63; 7,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-25,52; -2,18</t>
+          <t>-25,91; -2,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-88,23; -74,88</t>
+          <t>-87,85; -74,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 9,79</t>
+          <t>-5,06; 9,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,43; 4,03</t>
+          <t>-11,82; 3,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-83,23; -72,76</t>
+          <t>-82,95; -73,19</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 25,02</t>
+          <t>-4,44; 23,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 25,91</t>
+          <t>-5,08; 25,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,15; 11,14</t>
+          <t>-12,63; 9,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-29,63; -2,81</t>
+          <t>-30,39; -3,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 13,3</t>
+          <t>-6,2; 12,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-15,24; 5,42</t>
+          <t>-14,55; 5,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,83; -2,64</t>
+          <t>-8,83; -2,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,64; -8,08</t>
+          <t>-14,96; -8,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-96,03; -92,47</t>
+          <t>-96,09; -92,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,27; -2,01</t>
+          <t>-8,29; -2,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,33; -6,78</t>
+          <t>-13,59; -6,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-95,36; -91,69</t>
+          <t>-95,34; -91,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,49; -3,42</t>
+          <t>-7,76; -3,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,97; -8,44</t>
+          <t>-13,52; -8,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-95,18; -92,73</t>
+          <t>-95,26; -92,57</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,28; -2,94</t>
+          <t>-9,23; -2,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,4; -8,74</t>
+          <t>-15,74; -8,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,76; -2,19</t>
+          <t>-8,75; -2,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-14,21; -7,4</t>
+          <t>-14,39; -7,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-7,93; -3,65</t>
+          <t>-8,18; -3,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-13,66; -9,05</t>
+          <t>-14,22; -9,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 7,7</t>
+          <t>-0,38; 8,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 2,7</t>
+          <t>-7,7; 2,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-94,66; -87,4</t>
+          <t>-94,73; -87,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 2,37</t>
+          <t>-7,06; 2,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 0,12</t>
+          <t>-9,05; 0,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-96,73; -90,55</t>
+          <t>-96,94; -90,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 3,9</t>
+          <t>-2,46; 4,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 0,25</t>
+          <t>-7,0; 0,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-94,67; -90,06</t>
+          <t>-94,91; -89,97</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 8,72</t>
+          <t>-0,37; 9,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 3,05</t>
+          <t>-8,3; 2,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1230,12 +1230,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 2,57</t>
+          <t>-7,45; 2,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-9,62; 0,13</t>
+          <t>-9,5; 0,09</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1245,12 +1245,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 4,33</t>
+          <t>-2,61; 4,53</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 0,24</t>
+          <t>-7,41; 0,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 0,7</t>
+          <t>-4,45; 0,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,74; -3,9</t>
+          <t>-10,16; -4,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-92,75; -89,23</t>
+          <t>-92,76; -89,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,58; -1,52</t>
+          <t>-6,48; -1,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-11,34; -5,66</t>
+          <t>-11,36; -5,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-93,89; -90,54</t>
+          <t>-93,81; -90,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,76; -1,19</t>
+          <t>-4,89; -1,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-9,82; -5,87</t>
+          <t>-9,73; -5,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-92,94; -90,45</t>
+          <t>-92,94; -90,55</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 0,77</t>
+          <t>-4,85; 0,63</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-10,58; -4,37</t>
+          <t>-11,04; -4,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1446,12 +1446,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-7,05; -1,66</t>
+          <t>-6,94; -1,68</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-12,22; -6,19</t>
+          <t>-12,27; -6,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-5,14; -1,3</t>
+          <t>-5,27; -1,29</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,64; -6,43</t>
+          <t>-10,44; -6,47</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">

--- a/data/trans_camb/IP41-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP41-Estudios-trans_camb.xlsx
@@ -37,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -63,13 +63,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -504,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -515,9 +508,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -533,21 +523,18 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -564,37 +551,22 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2012/2007</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
+          <t>2016/2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>2012/2007</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
         </is>
       </c>
     </row>
@@ -607,9 +579,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -634,37 +603,22 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-74,41</t>
+          <t>-1,4</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,4</t>
+          <t>-14,05</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-14,05</t>
+          <t>2,6</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-82,14</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,6</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
           <t>-3,97</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>-78,28</t>
         </is>
       </c>
     </row>
@@ -677,47 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 15,99</t>
+          <t>-3,39; 16,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 17,48</t>
+          <t>-3,77; 18,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-81,56; -66,14</t>
+          <t>-12,02; 6,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,63; 7,85</t>
+          <t>-25,37; -2,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-25,91; -2,91</t>
+          <t>-3,89; 10,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-87,85; -74,19</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-5,06; 9,4</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-11,82; 3,91</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>-82,95; -73,19</t>
+          <t>-12,08; 4,85</t>
         </is>
       </c>
     </row>
@@ -740,37 +679,22 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-1,71%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,71%</t>
+          <t>-17,11%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-17,11%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>3,32%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
           <t>-5,07%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -783,47 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 23,1</t>
+          <t>-4,05; 24,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 25,72</t>
+          <t>-4,46; 28,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-14,06; 8,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 9,85</t>
+          <t>-29,61; -2,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-30,39; -3,69</t>
+          <t>-4,83; 14,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-6,2; 12,68</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-14,55; 5,22</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-14,67; 6,3</t>
         </is>
       </c>
     </row>
@@ -850,37 +759,22 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-94,42</t>
+          <t>-5,17</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-5,17</t>
+          <t>-10,04</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-10,04</t>
+          <t>-5,46</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-93,61</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-5,46</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
           <t>-10,78</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>-93,99</t>
         </is>
       </c>
     </row>
@@ -893,47 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,83; -2,67</t>
+          <t>-8,85; -2,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,96; -8,18</t>
+          <t>-15,19; -8,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-96,09; -92,35</t>
+          <t>-8,37; -2,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,29; -2,33</t>
+          <t>-13,32; -6,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,59; -6,98</t>
+          <t>-7,75; -3,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-95,34; -91,76</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-7,76; -3,42</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-13,52; -8,58</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>-95,26; -92,57</t>
+          <t>-13,11; -8,42</t>
         </is>
       </c>
     </row>
@@ -956,37 +835,22 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-5,53%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-5,53%</t>
+          <t>-10,73%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>-10,73%</t>
+          <t>-5,81%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-5,81%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
           <t>-11,47%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -999,47 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,23; -2,9</t>
+          <t>-9,3; -2,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,74; -8,78</t>
+          <t>-15,87; -8,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,9; -2,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,75; -2,51</t>
+          <t>-14,09; -7,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-14,39; -7,54</t>
+          <t>-8,18; -3,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-8,18; -3,65</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-14,22; -9,24</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-13,81; -9,0</t>
         </is>
       </c>
     </row>
@@ -1066,37 +915,22 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-91,53</t>
+          <t>-2,41</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-2,41</t>
+          <t>-4,39</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>-4,39</t>
+          <t>0,66</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-94,37</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,66</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
           <t>-3,46</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>-92,89</t>
         </is>
       </c>
     </row>
@@ -1109,47 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 8,1</t>
+          <t>-0,59; 8,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 2,45</t>
+          <t>-7,3; 2,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-94,73; -87,78</t>
+          <t>-7,49; 2,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 2,08</t>
+          <t>-9,45; -0,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 0,09</t>
+          <t>-2,12; 3,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-96,94; -90,7</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-2,46; 4,11</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-7,0; 0,34</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>-94,91; -89,97</t>
+          <t>-7,12; 0,41</t>
         </is>
       </c>
     </row>
@@ -1172,37 +991,22 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-2,55%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-2,55%</t>
+          <t>-4,65%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>-4,65%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
           <t>-3,72%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 9,22</t>
+          <t>-0,62; 9,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 2,74</t>
+          <t>-7,88; 3,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,9; 2,35</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 2,19</t>
+          <t>-9,77; -0,06</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 0,09</t>
+          <t>-2,25; 4,17</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-2,61; 4,53</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-7,41; 0,36</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-7,58; 0,43</t>
         </is>
       </c>
     </row>
@@ -1282,37 +1071,22 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-91,09</t>
+          <t>-4,02</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-4,02</t>
+          <t>-8,63</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>-8,63</t>
+          <t>-3,0</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-92,38</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-3,0</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
           <t>-7,79</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>-91,76</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 0,57</t>
+          <t>-4,54; 0,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,16; -4,17</t>
+          <t>-9,95; -4,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-92,76; -89,28</t>
+          <t>-6,59; -1,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,48; -1,55</t>
+          <t>-11,45; -6,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-11,36; -5,84</t>
+          <t>-4,6; -1,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-93,81; -90,74</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-4,89; -1,16</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-9,73; -5,93</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>-92,94; -90,55</t>
+          <t>-9,85; -5,86</t>
         </is>
       </c>
     </row>
@@ -1388,37 +1147,22 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-4,36%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-4,36%</t>
+          <t>-9,34%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>-9,34%</t>
+          <t>-3,27%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>-3,27%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
           <t>-8,49%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 0,63</t>
+          <t>-4,92; 0,77</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,04; -4,66</t>
+          <t>-10,78; -4,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,1; -1,69</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,94; -1,68</t>
+          <t>-12,24; -6,73</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-12,27; -6,45</t>
+          <t>-4,95; -1,25</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>-5,27; -1,29</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-10,44; -6,47</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-10,67; -6,47</t>
         </is>
       </c>
     </row>
@@ -1485,11 +1214,11 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A4:A7"/>
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A11"/>
-    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A12:A15"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A16:A19"/>
   </mergeCells>

--- a/data/trans_camb/IP41-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP41-Estudios-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-1,4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-14,05</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>6,59</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>7,08</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,4</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-14,05</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 16,15</t>
+          <t>-11,4; 8,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 18,37</t>
+          <t>-25,52; -2,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,02; 6,79</t>
+          <t>-3,16; 17,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-25,37; -2,25</t>
+          <t>-4,21; 17,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 10,52</t>
+          <t>-4,24; 9,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,08; 4,85</t>
+          <t>-12,43; 4,03</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-1,71%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-17,11%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>8,85%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>9,52%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-1,71%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-17,11%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 24,16</t>
+          <t>-13,15; 11,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 28,01</t>
+          <t>-29,63; -2,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-14,06; 8,63</t>
+          <t>-3,98; 25,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-29,61; -2,97</t>
+          <t>-5,34; 25,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 14,09</t>
+          <t>-5,14; 13,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-14,67; 6,3</t>
+          <t>-15,24; 5,42</t>
         </is>
       </c>
     </row>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-5,17</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-10,04</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-5,79</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-11,58</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-5,17</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-10,04</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,85; -2,72</t>
+          <t>-8,27; -2,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,19; -8,29</t>
+          <t>-13,33; -6,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,37; -2,44</t>
+          <t>-8,83; -2,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,32; -6,72</t>
+          <t>-14,64; -8,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,75; -3,44</t>
+          <t>-7,49; -3,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-13,11; -8,42</t>
+          <t>-12,97; -8,44</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-5,53%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-10,73%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-6,14%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>-12,27%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-5,53%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-10,73%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,3; -2,96</t>
+          <t>-8,76; -2,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,87; -8,82</t>
+          <t>-14,21; -7,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,9; -2,67</t>
+          <t>-9,28; -2,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,09; -7,32</t>
+          <t>-15,4; -8,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-8,18; -3,68</t>
+          <t>-7,93; -3,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-13,81; -9,0</t>
+          <t>-13,66; -9,05</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-2,41</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-4,39</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>3,64</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>-2,71</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-2,41</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-4,39</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 8,13</t>
+          <t>-6,75; 2,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 2,89</t>
+          <t>-9,23; 0,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 2,21</t>
+          <t>-0,52; 7,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,45; -0,08</t>
+          <t>-7,63; 2,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 3,8</t>
+          <t>-2,52; 3,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 0,41</t>
+          <t>-7,09; 0,25</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-2,55%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-4,65%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>3,98%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>-2,96%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-2,55%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-4,65%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 9,24</t>
+          <t>-7,07; 2,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 3,23</t>
+          <t>-9,62; 0,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 2,35</t>
+          <t>-0,54; 8,72</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,77; -0,06</t>
+          <t>-8,19; 3,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 4,17</t>
+          <t>-2,66; 4,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-7,58; 0,43</t>
+          <t>-7,61; 0,24</t>
         </is>
       </c>
     </row>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-4,02</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-8,63</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-1,92</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-6,9</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-4,02</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-8,63</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 0,7</t>
+          <t>-6,58; -1,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,95; -4,04</t>
+          <t>-11,34; -5,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,59; -1,53</t>
+          <t>-4,59; 0,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,45; -6,14</t>
+          <t>-9,74; -3,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,6; -1,14</t>
+          <t>-4,76; -1,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,85; -5,86</t>
+          <t>-9,82; -5,87</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-4,36%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-9,34%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-2,11%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>-7,57%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-4,36%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-9,34%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 0,77</t>
+          <t>-7,05; -1,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-10,78; -4,48</t>
+          <t>-12,22; -6,19</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-7,1; -1,69</t>
+          <t>-5,01; 0,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-12,24; -6,73</t>
+          <t>-10,58; -4,37</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-4,95; -1,25</t>
+          <t>-5,14; -1,3</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-10,67; -6,47</t>
+          <t>-10,64; -6,43</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP41-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP41-Estudios-trans_camb.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -118,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -131,6 +134,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -497,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -591,467 +600,319 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-1,4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-14,05</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6,59</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7,08</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,6</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-3,97</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-1.401101808319249</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-14.05045654127043</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>6.587598973037212</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>7.082068045808676</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>2.59556598522559</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-3.970263197879009</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-11,4; 8,5</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-25,52; -2,18</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-3,16; 17,05</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-4,21; 17,53</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-4,24; 9,79</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-12,43; 4,03</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-11.39699383970105</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-25.52381602175416</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-3.159052541019684</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-4.208757375848929</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-4.237955796945426</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-12.42729846828688</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-1,71%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-17,11%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>8,85%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>9,52%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,32%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-5,07%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>8.49781006445156</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>-2.181947602649305</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>17.04975701653417</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>17.52797123743688</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>9.79234674576232</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>4.03044599424054</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-13,15; 11,14</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-29,63; -2,81</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-3,98; 25,02</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-5,34; 25,91</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-5,14; 13,3</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-15,24; 5,42</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>-0.01705845573580283</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-0.1710647217453813</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0.08852857595203652</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.09517358319123696</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.0331591560547513</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.05072133696707534</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-5,17</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-10,04</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-5,79</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-11,58</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-5,46</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-10,78</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>-0.13146093894483</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.2963091200098144</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.03983932907258045</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.05339989340603865</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.05139624801069728</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.1524023067643432</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-8,27; -2,01</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-13,33; -6,78</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-8,83; -2,64</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-14,64; -8,08</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-7,49; -3,42</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-12,97; -8,44</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>0.1114032418967354</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>-0.0281278461631043</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.2502427629687844</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.259074732127734</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.1329747884181458</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.05420621267273509</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n"/>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-5,53%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-10,73%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-6,14%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-12,27%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-5,81%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-11,47%</t>
-        </is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>-5.174490071732785</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-10.04358940281589</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-5.793910864715479</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-11.58306147394627</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-5.461397714812676</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-10.78008934467134</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-8,76; -2,19</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-14,21; -7,4</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-9,28; -2,94</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-15,4; -8,74</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-7,93; -3,65</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-13,66; -9,05</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-8.271369672664159</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-13.33172080508897</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-8.829277504313202</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-14.64349118628878</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-7.485809279683886</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-12.9739438644945</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-2,41</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-4,39</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>3,64</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-2,71</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,66</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-3,46</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>-2.011090529249663</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>-6.7842623742335</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>-2.638085179425059</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>-8.078940416433975</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>-3.423422857146321</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>-8.436231350475373</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-6,75; 2,37</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-9,23; 0,12</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-0,52; 7,7</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-7,63; 2,7</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-2,52; 3,9</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-7,09; 0,25</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>-0.0552775638683053</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-0.1072927277827928</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.06136378543450594</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.1226771546125321</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.05810800112434265</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.1146976427044852</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-2,55%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-4,65%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-2,96%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-3,72%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>-0.08762657028484189</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.1421439054847671</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.09281608425221162</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.1539892379249493</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.0792698576958847</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.1366355291752273</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-7,07; 2,57</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-9,62; 0,13</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-0,54; 8,72</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-8,19; 3,05</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-2,66; 4,33</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-7,61; 0,24</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>-0.02185278033500046</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>-0.07395386934049908</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>-0.02936663976994374</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>-0.08736860465967626</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>-0.03654895889918076</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>-0.09045009233926483</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1059,153 +920,317 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-4,02</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-8,63</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-1,92</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-6,9</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-3,0</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-7,79</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>-2.408022967719436</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-4.386321566094287</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>3.643470083842493</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-2.708332553827275</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.6560474228765933</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-3.459559926864075</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-6,58; -1,52</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-11,34; -5,66</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-4,59; 0,7</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-9,74; -3,9</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-4,76; -1,19</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-9,82; -5,87</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-6.749360115946146</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-9.231867069372059</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.5192002519451314</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-7.633393119937383</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-2.516334435651523</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-7.088527020124468</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>-4,36%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-9,34%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-2,11%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-7,57%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-3,27%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-8,49%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>2.373513894691958</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.1208218863152592</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>7.703185723533649</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>2.700536634930396</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>3.904842632253649</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0.248738400369114</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>-7,05; -1,66</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>-12,22; -6,19</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>-5,01; 0,77</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>-10,58; -4,37</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>-5,14; -1,3</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-10,64; -6,43</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>-0.02551693927143513</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-0.04648024646252245</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0.03980415466548935</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-0.02958797118609221</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.007062761139821452</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.03724432801702406</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>-0.07069072421042349</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.09623998079436055</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.005407075333103611</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.08192992830888707</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.02658555744681226</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.07612364159010909</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>0.02574516522848391</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0.001252548472372936</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0.08721320394450348</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0.0304757451822395</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.04332528309272278</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.002446485812819987</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-4.024263812959927</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-8.628847447036447</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-1.920609471046919</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-6.899429795977785</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-3.004805749005846</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-7.790866449083445</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-6.582862565311902</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-11.34039483121496</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-4.586506288794669</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-9.739877218791429</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-4.759433259464915</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-9.822216582780467</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>-1.519867659829669</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>-5.655889151167134</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.697618110699702</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>-3.895826127379509</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>-1.186485517956407</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>-5.87246134205196</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n"/>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>-0.04356008133611498</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-0.09340175348826679</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-0.02108408304931155</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.07574061932121784</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.03274664380853521</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.08490556457847975</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>-0.0704936424278118</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-0.1221843592470575</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-0.05008384648096822</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.1058211348613063</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.05143561706738189</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.1064155499879359</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>-0.01664642179737377</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>-0.06187219891615017</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>0.00769912496708838</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>-0.04373754298627987</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>-0.01300892927480256</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>-0.06425273190914974</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1213,14 +1238,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A22:A27"/>
+    <mergeCell ref="A4:A9"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="A10:A15"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
